--- a/data/b2_candoi/B2 Candói 10-2025.xlsx
+++ b/data/b2_candoi/B2 Candói 10-2025.xlsx
@@ -4878,20 +4878,20 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>45933</v>
+        <v>45935</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1426.11</v>
+        <v>57245.94</v>
       </c>
     </row>
     <row r="3">
@@ -4900,52 +4900,52 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>57531.09</v>
+        <v>2923.82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>45935</v>
+        <v>45938</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Manutenção preventiva das bombas</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>2757.43</v>
+        <v>1923.95</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>45936</v>
+        <v>45939</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>2754.24</v>
+        <v>796.8200000000001</v>
       </c>
     </row>
     <row r="6">
@@ -4981,7 +4981,7 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>3930.02</v>
+        <v>4101.44</v>
       </c>
     </row>
     <row r="8">
@@ -4999,25 +4999,25 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1079.73</v>
+        <v>1021.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>45945</v>
+        <v>45943</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>8821.52</v>
+        <v>1052.77</v>
       </c>
     </row>
     <row r="10">
@@ -5026,106 +5026,106 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>798.91</v>
+        <v>8743.83</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>45949</v>
+        <v>45945</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>3786.9</v>
+        <v>1161.29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>45950</v>
+        <v>45949</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>20344.19</v>
+        <v>3891.34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>45951</v>
+        <v>45950</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>985.4</v>
+        <v>20242.95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>45954</v>
+        <v>45951</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Uniformes e EPI</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1124.53</v>
+        <v>1664.55</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>45955</v>
+        <v>45951</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fretes</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Frete das entregas de combustível</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>8690</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="16">
@@ -5134,16 +5134,16 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Fretes</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Frete das entregas de combustível</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>2619.06</v>
+        <v>8690</v>
       </c>
     </row>
     <row r="17">
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3782.14</v>
+        <v>3838.49</v>
       </c>
     </row>
     <row r="18">
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>2969.75</v>
+        <v>2825.96</v>
       </c>
     </row>
   </sheetData>
